--- a/data/trans_dic/P2A_senso_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P2A_senso_R-Provincia-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con limitación por discapacidad sensorial</t>
+          <t>Hogares con personas con limitación por discapacidad sensorial (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,33; 3,88</t>
+          <t>0,33; 3,6</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,59; 6,42</t>
+          <t>1,9; 6,88</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,63</t>
+          <t>0,0; 2,89</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,15</t>
+          <t>0,0; 2,9</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,4; 3,52</t>
+          <t>0,4; 3,39</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,72; 6,59</t>
+          <t>1,77; 6,54</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,72; 4,0</t>
+          <t>0,67; 3,85</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,81; 3,15</t>
+          <t>0,81; 3,21</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,52; 2,74</t>
+          <t>0,48; 2,84</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2,2; 5,62</t>
+          <t>2,14; 5,44</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,55; 2,52</t>
+          <t>0,65; 2,59</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,66; 2,54</t>
+          <t>0,65; 2,38</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,22; 4,31</t>
+          <t>1,22; 4,25</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,6; 3,27</t>
+          <t>0,61; 3,26</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,34</t>
+          <t>0,0; 1,46</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,29; 7,39</t>
+          <t>3,34; 7,34</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,81; 3,12</t>
+          <t>0,78; 2,99</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,96; 3,35</t>
+          <t>0,96; 3,31</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,43</t>
+          <t>0,0; 1,26</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,23; 7,48</t>
+          <t>4,32; 7,6</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,21; 3,04</t>
+          <t>1,2; 3,11</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,01; 2,8</t>
+          <t>1,0; 2,6</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,1; 0,94</t>
+          <t>0,1; 0,91</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,17; 6,73</t>
+          <t>4,13; 6,83</t>
         </is>
       </c>
     </row>
@@ -1002,57 +1002,57 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,63; 4,46</t>
+          <t>0,62; 4,68</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,47</t>
+          <t>0,0; 2,26</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,11; 4,46</t>
+          <t>1,03; 4,29</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,31</t>
+          <t>0,0; 1,81</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,29; 2,88</t>
+          <t>0,29; 2,84</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,62</t>
+          <t>0,0; 1,87</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,65; 2,63</t>
+          <t>0,63; 2,56</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,06</t>
+          <t>0,0; 1,03</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,74; 2,81</t>
+          <t>0,73; 2,75</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,14; 1,38</t>
+          <t>0,14; 1,41</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,09; 2,79</t>
+          <t>1,08; 3,01</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,24; 4,53</t>
+          <t>1,17; 4,6</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,29; 2,65</t>
+          <t>0,29; 2,46</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,24; 3,1</t>
+          <t>0,24; 3,26</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,92; 5,56</t>
+          <t>1,1; 5,94</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,5; 2,9</t>
+          <t>0,49; 2,95</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,73; 5,76</t>
+          <t>1,71; 5,62</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,87; 4,25</t>
+          <t>0,9; 4,68</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,67; 3,63</t>
+          <t>0,61; 4,18</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,99; 2,99</t>
+          <t>1,04; 2,99</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,2; 3,44</t>
+          <t>1,19; 3,31</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,82; 3,04</t>
+          <t>0,85; 3,0</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,99; 3,6</t>
+          <t>1,05; 3,56</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,33; 6,29</t>
+          <t>1,3; 6,15</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,75; 11,9</t>
+          <t>3,97; 11,7</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,62</t>
+          <t>0,0; 3,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,56</t>
+          <t>0,0; 2,33</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,55; 9,18</t>
+          <t>2,5; 9,03</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,11; 10,33</t>
+          <t>3,12; 9,95</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,86</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,91; 3,65</t>
+          <t>0,9; 3,48</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,62; 6,38</t>
+          <t>2,48; 6,39</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4,38; 9,6</t>
+          <t>4,26; 9,15</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,37</t>
+          <t>0,0; 1,25</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,8; 2,48</t>
+          <t>0,78; 2,44</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,87</t>
+          <t>0,0; 2,2</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,98</t>
+          <t>0,0; 2,29</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,98; 5,4</t>
+          <t>0,82; 5,51</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,41; 4,73</t>
+          <t>1,5; 5,3</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,72</t>
+          <t>0,0; 1,79</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,34; 2,93</t>
+          <t>0,34; 3,02</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,37; 3,28</t>
+          <t>0,35; 3,14</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2,67; 6,47</t>
+          <t>2,59; 6,54</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,29</t>
+          <t>0,0; 1,26</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,7</t>
+          <t>0,19; 1,84</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1,0; 3,42</t>
+          <t>0,91; 3,54</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2,32; 5,13</t>
+          <t>2,38; 5,03</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,86; 3,14</t>
+          <t>0,83; 3,02</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,45; 2,16</t>
+          <t>0,44; 2,04</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,65; 2,85</t>
+          <t>0,65; 2,73</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,28; 5,51</t>
+          <t>2,16; 5,27</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,94; 3,18</t>
+          <t>0,92; 2,97</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,05; 3,24</t>
+          <t>1,04; 3,31</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,64; 2,38</t>
+          <t>0,51; 2,47</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>5,1; 60,1</t>
+          <t>5,01; 63,88</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,11; 2,69</t>
+          <t>1,1; 2,57</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0,93; 2,39</t>
+          <t>0,93; 2,28</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,81; 2,2</t>
+          <t>0,74; 2,2</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>4,15; 49,74</t>
+          <t>4,07; 46,89</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,54; 2,05</t>
+          <t>0,53; 2,16</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,41; 1,9</t>
+          <t>0,4; 1,82</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,35; 1,89</t>
+          <t>0,35; 1,87</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,04; 0,93</t>
+          <t>0,05; 1,06</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,18; 3,3</t>
+          <t>1,22; 3,43</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,78; 2,48</t>
+          <t>0,78; 2,53</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,3; 1,65</t>
+          <t>0,33; 1,65</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,29; 1,24</t>
+          <t>0,3; 1,23</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1,04; 2,32</t>
+          <t>1,04; 2,34</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0,79; 1,87</t>
+          <t>0,73; 1,87</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0,44; 1,51</t>
+          <t>0,45; 1,46</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,24; 0,9</t>
+          <t>0,21; 0,85</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,16; 2,02</t>
+          <t>1,15; 2,03</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1,27; 2,19</t>
+          <t>1,27; 2,23</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,69; 1,47</t>
+          <t>0,68; 1,44</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,63; 2,76</t>
+          <t>1,69; 2,87</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,26; 2,17</t>
+          <t>1,28; 2,14</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,76; 2,76</t>
+          <t>1,76; 2,74</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,77; 1,47</t>
+          <t>0,75; 1,45</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2,79; 25,35</t>
+          <t>2,79; 25,2</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1,3; 1,92</t>
+          <t>1,32; 1,91</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1,61; 2,32</t>
+          <t>1,62; 2,3</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0,79; 1,31</t>
+          <t>0,81; 1,34</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>2,46; 15,39</t>
+          <t>2,47; 14,69</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con limitación por discapacidad sensorial</t>
+          <t>Hogares con personas con limitación por discapacidad sensorial (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>906; 10595</t>
+          <t>895; 9839</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>4689; 18907</t>
+          <t>5603; 20272</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 7739</t>
+          <t>0; 8486</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 9822</t>
+          <t>0; 9038</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1050; 9181</t>
+          <t>1045; 8854</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4949; 18926</t>
+          <t>5077; 18795</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2065; 11539</t>
+          <t>1920; 11105</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2344; 9117</t>
+          <t>2352; 9302</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2752; 14621</t>
+          <t>2541; 15146</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>12782; 32694</t>
+          <t>12451; 31657</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3194; 14664</t>
+          <t>3775; 15087</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>3978; 15265</t>
+          <t>3920; 14290</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5996; 21251</t>
+          <t>6029; 20956</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3021; 16513</t>
+          <t>3061; 16467</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 6710</t>
+          <t>0; 7330</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>17073; 38312</t>
+          <t>17295; 38035</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4066; 15742</t>
+          <t>3937; 15066</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5010; 17565</t>
+          <t>5023; 17358</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 7500</t>
+          <t>0; 6602</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>21798; 38521</t>
+          <t>22252; 39163</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>12102; 30333</t>
+          <t>12008; 31047</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>10386; 28844</t>
+          <t>10243; 26796</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1013; 9622</t>
+          <t>992; 9320</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>43091; 69497</t>
+          <t>42713; 70561</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 5579</t>
+          <t>0; 5588</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2043; 14441</t>
+          <t>1997; 15163</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 7881</t>
+          <t>0; 7196</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3497; 14091</t>
+          <t>3252; 13558</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 4403</t>
+          <t>0; 6066</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>982; 9824</t>
+          <t>987; 9683</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 5456</t>
+          <t>0; 6297</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2276; 9189</t>
+          <t>2187; 8942</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 6934</t>
+          <t>0; 6739</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4954; 18716</t>
+          <t>4832; 18301</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>897; 9034</t>
+          <t>892; 9203</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>7283; 18586</t>
+          <t>7158; 20029</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4436; 16254</t>
+          <t>4179; 16509</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1085; 9895</t>
+          <t>1069; 9210</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>898; 11475</t>
+          <t>904; 12047</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2878; 17369</t>
+          <t>3437; 18567</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1843; 10787</t>
+          <t>1812; 10973</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6730; 22394</t>
+          <t>6649; 21846</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3376; 16444</t>
+          <t>3468; 18124</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3171; 17252</t>
+          <t>2896; 19891</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>7259; 21808</t>
+          <t>7566; 21847</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>9191; 26221</t>
+          <t>9044; 25285</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>6192; 23008</t>
+          <t>6409; 22725</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>7807; 28399</t>
+          <t>8312; 28062</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2709; 12793</t>
+          <t>2640; 12507</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>7969; 25295</t>
+          <t>8450; 24871</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 5530</t>
+          <t>0; 6330</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 4567</t>
+          <t>0; 4162</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>5289; 19072</t>
+          <t>5201; 18760</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>6831; 22686</t>
+          <t>6846; 21855</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 1873</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>2351; 9444</t>
+          <t>2325; 9003</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>10751; 26236</t>
+          <t>10206; 26280</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>18945; 41494</t>
+          <t>18405; 39539</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0; 5879</t>
+          <t>0; 5381</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>3489; 10847</t>
+          <t>3399; 10696</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 5072</t>
+          <t>0; 5949</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 5416</t>
+          <t>0; 6281</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2591; 14206</t>
+          <t>2152; 14499</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3794; 12753</t>
+          <t>4055; 14281</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 4787</t>
+          <t>0; 4991</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>943; 8211</t>
+          <t>949; 8454</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1008; 8967</t>
+          <t>960; 8570</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>6858; 16624</t>
+          <t>6670; 16806</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0; 7057</t>
+          <t>0; 6907</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1040; 9425</t>
+          <t>1052; 10168</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>5356; 18344</t>
+          <t>4899; 18959</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>12196; 27010</t>
+          <t>12544; 26478</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>5280; 19322</t>
+          <t>5104; 18600</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>2989; 14305</t>
+          <t>2913; 13497</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>4298; 18704</t>
+          <t>4244; 17894</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>14248; 34415</t>
+          <t>13511; 32915</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>6012; 20274</t>
+          <t>5893; 18966</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>7287; 22460</t>
+          <t>7202; 22985</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>4406; 16425</t>
+          <t>3553; 17088</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>43349; 510427</t>
+          <t>42527; 542535</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>13874; 33668</t>
+          <t>13730; 32242</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>12629; 32401</t>
+          <t>12575; 30892</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>10958; 29707</t>
+          <t>9948; 29586</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>61164; 732909</t>
+          <t>59984; 690933</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>4001; 15277</t>
+          <t>3972; 16089</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3189; 14767</t>
+          <t>3126; 14155</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>2699; 14734</t>
+          <t>2718; 14557</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>382; 8669</t>
+          <t>422; 9849</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>9248; 25868</t>
+          <t>9553; 26838</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>6459; 20394</t>
+          <t>6409; 20865</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>2503; 13637</t>
+          <t>2698; 13662</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>2096; 8923</t>
+          <t>2138; 8822</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>15908; 35448</t>
+          <t>15908; 35685</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>12734; 29934</t>
+          <t>11745; 29937</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>7078; 24273</t>
+          <t>7156; 23463</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>3967; 14892</t>
+          <t>3482; 13942</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>38003; 66259</t>
+          <t>37661; 66661</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>43387; 75044</t>
+          <t>43454; 76525</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>23416; 50009</t>
+          <t>22996; 48808</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>56418; 95588</t>
+          <t>58510; 99242</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>42733; 73473</t>
+          <t>43136; 72447</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>62677; 98308</t>
+          <t>62695; 97628</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>27272; 52016</t>
+          <t>26546; 51329</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>103513; 941132</t>
+          <t>103528; 935404</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>86200; 127504</t>
+          <t>87814; 127417</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>112471; 161895</t>
+          <t>113441; 160581</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>54633; 90956</t>
+          <t>56035; 93225</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>176341; 1103892</t>
+          <t>177115; 1053611</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P2A_senso_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P2A_senso_R-Provincia-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,2%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,33; 3,6</t>
+          <t>0,33; 3,65</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,9; 6,88</t>
+          <t>1,91; 6,42</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,89</t>
+          <t>0,0; 2,55</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,9</t>
+          <t>0,0; 2,21</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,4; 3,39</t>
+          <t>0,4; 3,4</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,77; 6,54</t>
+          <t>1,89; 6,61</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,67; 3,85</t>
+          <t>0,67; 3,96</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,81; 3,21</t>
+          <t>0,86; 3,05</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,48; 2,84</t>
+          <t>0,51; 2,96</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2,14; 5,44</t>
+          <t>2,12; 5,51</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,65; 2,59</t>
+          <t>0,64; 2,62</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,65; 2,38</t>
+          <t>0,69; 2,27</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,34%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,22; 4,25</t>
+          <t>1,2; 4,01</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,61; 3,26</t>
+          <t>0,6; 3,21</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
+          <t>0,0; 1,39</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>3,09; 7,16</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,78; 3,1</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,98; 3,51</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
           <t>0,0; 1,46</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>3,34; 7,34</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>0,78; 2,99</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0,96; 3,31</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 1,26</t>
-        </is>
-      </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,32; 7,6</t>
+          <t>4,3; 7,58</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,2; 3,11</t>
+          <t>1,19; 3,14</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,0; 2,6</t>
+          <t>1,01; 2,68</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,1; 0,91</t>
+          <t>0,11; 1,01</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,13; 6,83</t>
+          <t>4,2; 6,74</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,79%</t>
         </is>
       </c>
     </row>
@@ -1002,27 +1002,27 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,62; 4,68</t>
+          <t>0,62; 4,78</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,26</t>
+          <t>0,0; 2,46</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,03; 4,29</t>
+          <t>1,15; 4,29</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,81</t>
+          <t>0,0; 1,38</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,29; 2,84</t>
+          <t>0,29; 2,85</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1032,27 +1032,27 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,63; 2,56</t>
+          <t>0,67; 2,47</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,03</t>
+          <t>0,0; 0,98</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,73; 2,75</t>
+          <t>0,75; 2,9</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,14; 1,41</t>
+          <t>0,14; 1,46</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,08; 3,01</t>
+          <t>1,09; 2,9</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,07%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,17; 4,6</t>
+          <t>1,17; 4,58</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,29; 2,46</t>
+          <t>0,29; 2,45</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,24; 3,26</t>
+          <t>0,24; 2,91</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,1; 5,94</t>
+          <t>0,84; 4,82</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,49; 2,95</t>
+          <t>0,49; 2,87</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,71; 5,62</t>
+          <t>1,52; 5,43</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,9; 4,68</t>
+          <t>1,06; 4,93</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,61; 4,18</t>
+          <t>0,89; 4,75</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,04; 2,99</t>
+          <t>1,03; 3,1</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,19; 3,31</t>
+          <t>1,13; 3,39</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,85; 3,0</t>
+          <t>0,81; 2,98</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,05; 3,56</t>
+          <t>1,11; 3,9</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,59%</t>
         </is>
       </c>
     </row>
@@ -1277,17 +1277,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,3; 6,15</t>
+          <t>1,29; 5,84</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,97; 11,7</t>
+          <t>3,8; 11,57</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,0</t>
+          <t>0,0; 2,78</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1297,12 +1297,12 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,5; 9,03</t>
+          <t>2,6; 9,17</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,12; 9,95</t>
+          <t>2,78; 9,68</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1312,27 +1312,27 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,9; 3,48</t>
+          <t>1,39; 4,15</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,48; 6,39</t>
+          <t>2,39; 6,2</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4,26; 9,15</t>
+          <t>4,37; 9,13</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,25</t>
+          <t>0,0; 1,44</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,78; 2,44</t>
+          <t>0,89; 2,54</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,51%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,2</t>
+          <t>0,0; 1,52</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,29</t>
+          <t>0,0; 1,6</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,82; 5,51</t>
+          <t>1,11; 5,16</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,5; 5,3</t>
+          <t>1,47; 5,06</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,79</t>
+          <t>0,0; 2,06</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,34; 3,02</t>
+          <t>0,33; 2,98</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,35; 3,14</t>
+          <t>0,37; 3,69</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2,59; 6,54</t>
+          <t>2,47; 6,25</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,26</t>
+          <t>0,0; 1,09</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,84</t>
+          <t>0,19; 1,86</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,91; 3,54</t>
+          <t>0,92; 3,5</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2,38; 5,03</t>
+          <t>2,36; 4,98</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>28,28%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>5,26%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,83; 3,02</t>
+          <t>0,86; 3,06</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,44; 2,04</t>
+          <t>0,48; 2,3</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,65; 2,73</t>
+          <t>0,64; 2,84</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,16; 5,27</t>
+          <t>2,75; 6,21</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,92; 2,97</t>
+          <t>0,92; 3,06</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,04; 3,31</t>
+          <t>1,04; 3,32</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,51; 2,47</t>
+          <t>0,61; 2,46</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>5,01; 63,88</t>
+          <t>4,94; 8,05</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,1; 2,57</t>
+          <t>1,07; 2,57</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0,93; 2,28</t>
+          <t>0,9; 2,37</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,74; 2,2</t>
+          <t>0,78; 2,23</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>4,07; 46,89</t>
+          <t>4,16; 6,5</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,67%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,53; 2,16</t>
+          <t>0,52; 2,2</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,4; 1,82</t>
+          <t>0,4; 1,77</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,35; 1,87</t>
+          <t>0,35; 2,0</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,05; 1,06</t>
+          <t>0,15; 1,58</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,22; 3,43</t>
+          <t>1,18; 3,31</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,78; 2,53</t>
+          <t>0,76; 2,39</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,33; 1,65</t>
+          <t>0,3; 1,63</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,3; 1,23</t>
+          <t>0,31; 1,26</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1,04; 2,34</t>
+          <t>1,0; 2,4</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0,73; 1,87</t>
+          <t>0,67; 1,82</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0,45; 1,46</t>
+          <t>0,45; 1,43</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,21; 0,85</t>
+          <t>0,36; 1,23</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>2,87%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,15; 2,03</t>
+          <t>1,15; 2,0</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1,27; 2,23</t>
+          <t>1,25; 2,2</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,68; 1,44</t>
+          <t>0,67; 1,48</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,69; 2,87</t>
+          <t>1,96; 3,12</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,28; 2,14</t>
+          <t>1,27; 2,18</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,76; 2,74</t>
+          <t>1,72; 2,72</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,75; 1,45</t>
+          <t>0,74; 1,44</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2,79; 25,2</t>
+          <t>2,75; 3,79</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1,32; 1,91</t>
+          <t>1,32; 1,92</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1,62; 2,3</t>
+          <t>1,6; 2,33</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0,81; 1,34</t>
+          <t>0,78; 1,31</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>2,47; 14,69</t>
+          <t>2,55; 3,28</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2555</t>
+          <t>2099</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4981</t>
+          <t>5520</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>7536</t>
+          <t>7619</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>895; 9839</t>
+          <t>902; 9975</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>5603; 20272</t>
+          <t>5639; 18908</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 8486</t>
+          <t>0; 7479</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 9038</t>
+          <t>0; 7036</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1045; 8854</t>
+          <t>1056; 8869</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5077; 18795</t>
+          <t>5422; 18974</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1920; 11105</t>
+          <t>1934; 11435</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2352; 9302</t>
+          <t>2730; 9651</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2541; 15146</t>
+          <t>2721; 15779</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>12451; 31657</t>
+          <t>12362; 32040</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3775; 15087</t>
+          <t>3736; 15272</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>3920; 14290</t>
+          <t>4387; 14410</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>25608</t>
+          <t>26005</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>29456</t>
+          <t>31504</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>55064</t>
+          <t>57509</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6029; 20956</t>
+          <t>5938; 19795</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3061; 16467</t>
+          <t>3045; 16249</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 7330</t>
+          <t>0; 7010</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>17295; 38035</t>
+          <t>16400; 37997</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3937; 15066</t>
+          <t>3931; 15605</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5023; 17358</t>
+          <t>5109; 18361</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 6602</t>
+          <t>0; 7658</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>22252; 39163</t>
+          <t>23499; 41434</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>12008; 31047</t>
+          <t>11913; 31310</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>10243; 26796</t>
+          <t>10400; 27590</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>992; 9320</t>
+          <t>1161; 10325</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>42713; 70561</t>
+          <t>45222; 72558</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7370</t>
+          <t>7213</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4846</t>
+          <t>4827</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>12216</t>
+          <t>12040</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 5588</t>
+          <t>0; 5578</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1997; 15163</t>
+          <t>2011; 15497</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 7196</t>
+          <t>0; 7844</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3252; 13558</t>
+          <t>3622; 13565</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 6066</t>
+          <t>0; 4634</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>987; 9683</t>
+          <t>978; 9722</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 6297</t>
+          <t>0; 6302</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2187; 8942</t>
+          <t>2403; 8795</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 6739</t>
+          <t>0; 6402</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4832; 18301</t>
+          <t>4996; 19282</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>892; 9203</t>
+          <t>897; 9581</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>7158; 20029</t>
+          <t>7338; 19471</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>7675</t>
+          <t>8477</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>7372</t>
+          <t>7985</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>15047</t>
+          <t>16462</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4179; 16509</t>
+          <t>4184; 16429</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1069; 9210</t>
+          <t>1082; 9144</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>904; 12047</t>
+          <t>900; 10770</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3437; 18567</t>
+          <t>3152; 17996</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1812; 10973</t>
+          <t>1833; 10667</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6649; 21846</t>
+          <t>5921; 21119</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3468; 18124</t>
+          <t>4098; 19077</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2896; 19891</t>
+          <t>3735; 20034</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>7566; 21847</t>
+          <t>7540; 22629</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>9044; 25285</t>
+          <t>8586; 25862</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>6409; 22725</t>
+          <t>6149; 22554</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>8312; 28062</t>
+          <t>8789; 30972</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1177</t>
+          <t>1253</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>5252</t>
+          <t>5673</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>6429</t>
+          <t>6926</t>
         </is>
       </c>
     </row>
@@ -3041,32 +3041,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2640; 12507</t>
+          <t>2628; 11867</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>8450; 24871</t>
+          <t>8080; 24606</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 6330</t>
+          <t>0; 5865</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 4162</t>
+          <t>0; 4800</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>5201; 18760</t>
+          <t>5395; 19042</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>6846; 21855</t>
+          <t>6114; 21249</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -3076,27 +3076,27 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>2325; 9003</t>
+          <t>3172; 9501</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>10206; 26280</t>
+          <t>9838; 25474</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>18405; 39539</t>
+          <t>18879; 39455</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0; 5381</t>
+          <t>0; 6183</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>3399; 10696</t>
+          <t>3870; 11017</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>7402</t>
+          <t>7947</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>10747</t>
+          <t>10801</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>18149</t>
+          <t>18748</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 5949</t>
+          <t>0; 4123</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 6281</t>
+          <t>0; 4376</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2152; 14499</t>
+          <t>2910; 13570</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4055; 14281</t>
+          <t>3969; 13696</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 4991</t>
+          <t>0; 5721</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>949; 8454</t>
+          <t>936; 8339</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>960; 8570</t>
+          <t>1010; 10069</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>6670; 16806</t>
+          <t>6517; 16497</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0; 6907</t>
+          <t>0; 5991</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1052; 10168</t>
+          <t>1058; 10328</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>4899; 18959</t>
+          <t>4933; 18777</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>12544; 26478</t>
+          <t>12633; 26622</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>21750</t>
+          <t>29837</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>240185</t>
+          <t>48614</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>261934</t>
+          <t>78452</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>5104; 18600</t>
+          <t>5299; 18809</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>2913; 13497</t>
+          <t>3176; 15242</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>4244; 17894</t>
+          <t>4194; 18661</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>13511; 32915</t>
+          <t>19802; 44718</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>5893; 18966</t>
+          <t>5871; 19533</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>7202; 22985</t>
+          <t>7215; 23012</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>3553; 17088</t>
+          <t>4185; 17024</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>42527; 542535</t>
+          <t>38103; 62138</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>13730; 32242</t>
+          <t>13404; 32149</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>12575; 30892</t>
+          <t>12267; 32147</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>9948; 29586</t>
+          <t>10560; 30013</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>59984; 690933</t>
+          <t>62064; 96920</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3218</t>
+          <t>5174</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>4616</t>
+          <t>5761</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>7833</t>
+          <t>10935</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>3972; 16089</t>
+          <t>3891; 16350</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3126; 14155</t>
+          <t>3093; 13752</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>2718; 14557</t>
+          <t>2716; 15600</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>422; 9849</t>
+          <t>1194; 12618</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>9553; 26838</t>
+          <t>9222; 25922</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>6409; 20865</t>
+          <t>6231; 19724</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>2698; 13662</t>
+          <t>2471; 13441</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>2138; 8822</t>
+          <t>2595; 10474</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>15908; 35685</t>
+          <t>15206; 36662</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>11745; 29937</t>
+          <t>10702; 29107</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>7156; 23463</t>
+          <t>7233; 22972</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>3482; 13942</t>
+          <t>5872; 19981</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>76755</t>
+          <t>88005</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>307454</t>
+          <t>120685</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>384209</t>
+          <t>208690</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>37661; 66661</t>
+          <t>37702; 65606</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>43454; 76525</t>
+          <t>42672; 75290</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>22996; 48808</t>
+          <t>22904; 50111</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>58510; 99242</t>
+          <t>69106; 110224</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>43136; 72447</t>
+          <t>43055; 73542</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>62695; 97628</t>
+          <t>61273; 96951</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>26546; 51329</t>
+          <t>26305; 51035</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>103528; 935404</t>
+          <t>102653; 141561</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>87814; 127417</t>
+          <t>87785; 127834</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>113441; 160581</t>
+          <t>112025; 162776</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>56035; 93225</t>
+          <t>54381; 90609</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>177115; 1053611</t>
+          <t>185026; 238607</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P2A_senso_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P2A_senso_R-Provincia-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con limitación por discapacidad sensorial (tasa de respuesta: 100,0%)</t>
+          <t>Población que convive con personas con alguna limitación por discapacidad sensorial (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1951,7 +1951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con limitación por discapacidad sensorial (tasa de respuesta: 100,0%)</t>
+          <t>Población que convive con personas con alguna limitación por discapacidad sensorial (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
